--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/168.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/168.xlsx
@@ -426,13 +426,13 @@
         <v>-5.209818436163975</v>
       </c>
       <c r="E2">
-        <v>-5.594148287181001</v>
+        <v>-5.841593163908125</v>
       </c>
       <c r="F2">
-        <v>-4.278766224273491</v>
+        <v>-4.017664589259778</v>
       </c>
       <c r="G2">
-        <v>-12.66420509368834</v>
+        <v>-13.00967045234791</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.332227680679934</v>
       </c>
       <c r="E3">
-        <v>-7.005379284561354</v>
+        <v>-8.029788032206504</v>
       </c>
       <c r="F3">
-        <v>-3.986650876317727</v>
+        <v>-3.767476271709358</v>
       </c>
       <c r="G3">
-        <v>-13.01179251203858</v>
+        <v>-11.63880333944556</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.561746934615881</v>
       </c>
       <c r="E4">
-        <v>-6.15928825791624</v>
+        <v>-8.663249090295464</v>
       </c>
       <c r="F4">
-        <v>-4.361099927405356</v>
+        <v>-3.902931430509851</v>
       </c>
       <c r="G4">
-        <v>-12.51064212830371</v>
+        <v>-11.96628581473581</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.847538016910765</v>
       </c>
       <c r="E5">
-        <v>-7.144901568737677</v>
+        <v>-8.114379926669786</v>
       </c>
       <c r="F5">
-        <v>-4.250245264442341</v>
+        <v>-3.771726146533439</v>
       </c>
       <c r="G5">
-        <v>-12.26917755776035</v>
+        <v>-11.62762031661391</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.147270842440594</v>
       </c>
       <c r="E6">
-        <v>-8.499200590893597</v>
+        <v>-9.865187604463314</v>
       </c>
       <c r="F6">
-        <v>-4.036435463622523</v>
+        <v>-3.671266137346411</v>
       </c>
       <c r="G6">
-        <v>-11.96973209264219</v>
+        <v>-10.70905979856003</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.413002502615874</v>
       </c>
       <c r="E7">
-        <v>-8.759855026301095</v>
+        <v>-9.605044886618684</v>
       </c>
       <c r="F7">
-        <v>-4.206802627475922</v>
+        <v>-3.124909768402618</v>
       </c>
       <c r="G7">
-        <v>-11.88537608175602</v>
+        <v>-12.49556921446341</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.605555213953226</v>
       </c>
       <c r="E8">
-        <v>-10.05415176785538</v>
+        <v>-10.92089716444948</v>
       </c>
       <c r="F8">
-        <v>-4.176225225513575</v>
+        <v>-3.3769866552572</v>
       </c>
       <c r="G8">
-        <v>-11.6263556882179</v>
+        <v>-12.3865860553106</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.688778864926233</v>
       </c>
       <c r="E9">
-        <v>-9.459123868669522</v>
+        <v>-9.986460138388727</v>
       </c>
       <c r="F9">
-        <v>-3.86460099623847</v>
+        <v>-3.399657405436715</v>
       </c>
       <c r="G9">
-        <v>-11.348385732013</v>
+        <v>-11.34733959962259</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.642442060962794</v>
       </c>
       <c r="E10">
-        <v>-10.58168276195692</v>
+        <v>-11.80724632502279</v>
       </c>
       <c r="F10">
-        <v>-3.900452930752189</v>
+        <v>-3.248283626627182</v>
       </c>
       <c r="G10">
-        <v>-11.27396797883572</v>
+        <v>-10.91065877971949</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.468743568543311</v>
       </c>
       <c r="E11">
-        <v>-11.13880280522457</v>
+        <v>-12.49264897997972</v>
       </c>
       <c r="F11">
-        <v>-3.760401857385089</v>
+        <v>-3.487851612308665</v>
       </c>
       <c r="G11">
-        <v>-10.63749242509206</v>
+        <v>-11.14793219961013</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.187933556158469</v>
       </c>
       <c r="E12">
-        <v>-11.86817241432198</v>
+        <v>-12.52208858950359</v>
       </c>
       <c r="F12">
-        <v>-3.840793937064627</v>
+        <v>-3.215046390579854</v>
       </c>
       <c r="G12">
-        <v>-10.5324587467676</v>
+        <v>-9.529158194545001</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.834554066205631</v>
       </c>
       <c r="E13">
-        <v>-12.55861526084946</v>
+        <v>-13.27628782158506</v>
       </c>
       <c r="F13">
-        <v>-3.774263243409973</v>
+        <v>-2.9474167197827</v>
       </c>
       <c r="G13">
-        <v>-9.477573273952077</v>
+        <v>-9.762220600509693</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.465897650343824</v>
       </c>
       <c r="E14">
-        <v>-14.16488310526617</v>
+        <v>-14.61971397764856</v>
       </c>
       <c r="F14">
-        <v>-3.214812002104369</v>
+        <v>-3.403317349807295</v>
       </c>
       <c r="G14">
-        <v>-8.688554402849878</v>
+        <v>-9.318061258233373</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.143037721815086</v>
       </c>
       <c r="E15">
-        <v>-14.0754004588746</v>
+        <v>-15.84447147234106</v>
       </c>
       <c r="F15">
-        <v>-3.294176256644786</v>
+        <v>-2.992759803847647</v>
       </c>
       <c r="G15">
-        <v>-8.929966004664612</v>
+        <v>-9.227425142459207</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.917891052887153</v>
       </c>
       <c r="E16">
-        <v>-14.64366960514914</v>
+        <v>-14.76041819354089</v>
       </c>
       <c r="F16">
-        <v>-2.855142886472578</v>
+        <v>-2.581716060171957</v>
       </c>
       <c r="G16">
-        <v>-8.244216291114439</v>
+        <v>-7.809147706888959</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.826731740778408</v>
       </c>
       <c r="E17">
-        <v>-16.49240553335854</v>
+        <v>-17.17925277152392</v>
       </c>
       <c r="F17">
-        <v>-2.774462572316431</v>
+        <v>-2.588396131723281</v>
       </c>
       <c r="G17">
-        <v>-8.045821918036996</v>
+        <v>-8.948104483674278</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.882489053600571</v>
       </c>
       <c r="E18">
-        <v>-17.08514655317052</v>
+        <v>-18.42663452235875</v>
       </c>
       <c r="F18">
-        <v>-2.69097751498404</v>
+        <v>-2.226475778132693</v>
       </c>
       <c r="G18">
-        <v>-7.959340536914614</v>
+        <v>-7.697579011669981</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.07028175132533</v>
       </c>
       <c r="E19">
-        <v>-17.15197324410172</v>
+        <v>-18.51050638945481</v>
       </c>
       <c r="F19">
-        <v>-2.074666480196413</v>
+        <v>-1.965194392497577</v>
       </c>
       <c r="G19">
-        <v>-7.490318997638369</v>
+        <v>-7.622899725395102</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.354887167095232</v>
       </c>
       <c r="E20">
-        <v>-17.86470523969495</v>
+        <v>-18.4421943590491</v>
       </c>
       <c r="F20">
-        <v>-1.932843239909938</v>
+        <v>-1.641623477649355</v>
       </c>
       <c r="G20">
-        <v>-7.927168655363976</v>
+        <v>-7.715465889218663</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.698938468275501</v>
       </c>
       <c r="E21">
-        <v>-18.6553813299082</v>
+        <v>-19.75258076875264</v>
       </c>
       <c r="F21">
-        <v>-1.893600591031264</v>
+        <v>-1.418968679291808</v>
       </c>
       <c r="G21">
-        <v>-7.914989158324998</v>
+        <v>-8.175999189732217</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.057099988968708</v>
       </c>
       <c r="E22">
-        <v>-19.11996653530312</v>
+        <v>-20.90019570872448</v>
       </c>
       <c r="F22">
-        <v>-1.460724669458284</v>
+        <v>-1.417448321612986</v>
       </c>
       <c r="G22">
-        <v>-8.454323374309825</v>
+        <v>-7.608829906853199</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.383905995866943</v>
       </c>
       <c r="E23">
-        <v>-18.73623723331515</v>
+        <v>-21.42766783266391</v>
       </c>
       <c r="F23">
-        <v>-1.285818604451236</v>
+        <v>-1.190709937552478</v>
       </c>
       <c r="G23">
-        <v>-8.613312323833323</v>
+        <v>-7.678990298466973</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.650689595676226</v>
       </c>
       <c r="E24">
-        <v>-18.61304462641049</v>
+        <v>-20.67920164867616</v>
       </c>
       <c r="F24">
-        <v>-1.577140515743365</v>
+        <v>-1.14392964036927</v>
       </c>
       <c r="G24">
-        <v>-8.474901725381933</v>
+        <v>-8.774062483583714</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.839354652271367</v>
       </c>
       <c r="E25">
-        <v>-19.6239132367727</v>
+        <v>-21.08870702471578</v>
       </c>
       <c r="F25">
-        <v>-0.9344853249053606</v>
+        <v>-1.134592110291839</v>
       </c>
       <c r="G25">
-        <v>-9.10362729201816</v>
+        <v>-8.683055586709148</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.943426846593264</v>
       </c>
       <c r="E26">
-        <v>-19.7865035675441</v>
+        <v>-20.71402561379514</v>
       </c>
       <c r="F26">
-        <v>-0.9677122668642379</v>
+        <v>-1.443090104089866</v>
       </c>
       <c r="G26">
-        <v>-9.326916967550924</v>
+        <v>-8.836032585533331</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.970436652518943</v>
       </c>
       <c r="E27">
-        <v>-19.50913453457429</v>
+        <v>-19.84673680032012</v>
       </c>
       <c r="F27">
-        <v>-1.212158066765274</v>
+        <v>-0.9487101714378378</v>
       </c>
       <c r="G27">
-        <v>-8.644742643183164</v>
+        <v>-9.224058317645769</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.938525800871863</v>
       </c>
       <c r="E28">
-        <v>-18.59775196968659</v>
+        <v>-20.18887206854764</v>
       </c>
       <c r="F28">
-        <v>-0.9981154611758867</v>
+        <v>-1.177484409452643</v>
       </c>
       <c r="G28">
-        <v>-9.022740732857148</v>
+        <v>-8.633106075612625</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.866000557039402</v>
       </c>
       <c r="E29">
-        <v>-19.45664499235139</v>
+        <v>-20.46069372085805</v>
       </c>
       <c r="F29">
-        <v>-1.027547843761371</v>
+        <v>-0.9125525816824397</v>
       </c>
       <c r="G29">
-        <v>-9.603082676436927</v>
+        <v>-9.493212291079594</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.76837761266845</v>
       </c>
       <c r="E30">
-        <v>-18.9331579255387</v>
+        <v>-20.06659874186653</v>
       </c>
       <c r="F30">
-        <v>-1.016995611246798</v>
+        <v>-0.9765865629614029</v>
       </c>
       <c r="G30">
-        <v>-9.825620858132275</v>
+        <v>-9.020267755339312</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.667349162908598</v>
       </c>
       <c r="E31">
-        <v>-18.82648972028802</v>
+        <v>-20.00816784174556</v>
       </c>
       <c r="F31">
-        <v>-1.215312017095872</v>
+        <v>-0.8240416336274021</v>
       </c>
       <c r="G31">
-        <v>-9.276235825890222</v>
+        <v>-8.794760014295237</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.576827884830141</v>
       </c>
       <c r="E32">
-        <v>-18.64216724275382</v>
+        <v>-18.90134086716081</v>
       </c>
       <c r="F32">
-        <v>-1.046160347532573</v>
+        <v>-1.083698928846234</v>
       </c>
       <c r="G32">
-        <v>-9.66356965398495</v>
+        <v>-8.779276592808067</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.502393665265273</v>
       </c>
       <c r="E33">
-        <v>-17.74194736629502</v>
+        <v>-19.28732534920459</v>
       </c>
       <c r="F33">
-        <v>-0.8369987235745699</v>
+        <v>-1.215072877502641</v>
       </c>
       <c r="G33">
-        <v>-9.203440240027186</v>
+        <v>-8.952143349232189</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.449757702713648</v>
       </c>
       <c r="E34">
-        <v>-18.26772131248158</v>
+        <v>-18.29006027476142</v>
       </c>
       <c r="F34">
-        <v>-0.685076190665337</v>
+        <v>-0.5629930527618563</v>
       </c>
       <c r="G34">
-        <v>-9.255683959182425</v>
+        <v>-8.547611237060947</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.419173546704785</v>
       </c>
       <c r="E35">
-        <v>-17.86153983636359</v>
+        <v>-17.83979410417875</v>
       </c>
       <c r="F35">
-        <v>-0.8797627425562237</v>
+        <v>-0.887847561254542</v>
       </c>
       <c r="G35">
-        <v>-8.524189127370603</v>
+        <v>-9.065542776134384</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.403750265116151</v>
       </c>
       <c r="E36">
-        <v>-17.15392501639902</v>
+        <v>-17.49906719136763</v>
       </c>
       <c r="F36">
-        <v>-1.126825616482524</v>
+        <v>-0.4219537469035231</v>
       </c>
       <c r="G36">
-        <v>-8.402662311169497</v>
+        <v>-7.875057358030309</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.394754719434759</v>
       </c>
       <c r="E37">
-        <v>-16.23123032344016</v>
+        <v>-16.56645061185796</v>
       </c>
       <c r="F37">
-        <v>-0.5401449275198114</v>
+        <v>-0.7543696592894745</v>
       </c>
       <c r="G37">
-        <v>-8.275719442466144</v>
+        <v>-9.107209302291652</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.387941434665428</v>
       </c>
       <c r="E38">
-        <v>-15.27305503663119</v>
+        <v>-16.30115449059259</v>
       </c>
       <c r="F38">
-        <v>-0.8080842128234342</v>
+        <v>-1.079871111648617</v>
       </c>
       <c r="G38">
-        <v>-8.400801784576426</v>
+        <v>-8.474762682469285</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.374994274200493</v>
       </c>
       <c r="E39">
-        <v>-15.38856735161885</v>
+        <v>-15.6862692328831</v>
       </c>
       <c r="F39">
-        <v>-0.783737109932426</v>
+        <v>-0.4493003887983738</v>
       </c>
       <c r="G39">
-        <v>-8.158820768928939</v>
+        <v>-7.021595407460658</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.344995760176535</v>
       </c>
       <c r="E40">
-        <v>-15.1367977822144</v>
+        <v>-15.29216519694356</v>
       </c>
       <c r="F40">
-        <v>-0.6944058022131907</v>
+        <v>-0.6636090569815553</v>
       </c>
       <c r="G40">
-        <v>-7.43730392137248</v>
+        <v>-8.13460743885471</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.297839944523422</v>
       </c>
       <c r="E41">
-        <v>-14.60929395895691</v>
+        <v>-15.61329287424949</v>
       </c>
       <c r="F41">
-        <v>-1.178956464101044</v>
+        <v>-0.3760840806216927</v>
       </c>
       <c r="G41">
-        <v>-8.085353142321432</v>
+        <v>-7.720166863884428</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.23201023450613</v>
       </c>
       <c r="E42">
-        <v>-15.49137276854098</v>
+        <v>-15.56511443928189</v>
       </c>
       <c r="F42">
-        <v>-1.121578798784673</v>
+        <v>-0.7219931674071882</v>
       </c>
       <c r="G42">
-        <v>-7.067701375186087</v>
+        <v>-8.327966472166921</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.143944830659664</v>
       </c>
       <c r="E43">
-        <v>-13.40808000063029</v>
+        <v>-14.94174734975602</v>
       </c>
       <c r="F43">
-        <v>-0.779792890350024</v>
+        <v>-0.8973862219832338</v>
       </c>
       <c r="G43">
-        <v>-7.363200670021434</v>
+        <v>-7.385738864052792</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.035375871953035</v>
       </c>
       <c r="E44">
-        <v>-13.41475497131759</v>
+        <v>-13.70802347652833</v>
       </c>
       <c r="F44">
-        <v>-1.093874239352933</v>
+        <v>-1.070269102683308</v>
       </c>
       <c r="G44">
-        <v>-7.554891188381853</v>
+        <v>-7.777383022439652</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.910475238795017</v>
       </c>
       <c r="E45">
-        <v>-13.17408922017995</v>
+        <v>-13.4184185067898</v>
       </c>
       <c r="F45">
-        <v>-1.041391809021185</v>
+        <v>-0.6491830797978173</v>
       </c>
       <c r="G45">
-        <v>-7.661020657279809</v>
+        <v>-7.524166015231877</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.772250318606748</v>
       </c>
       <c r="E46">
-        <v>-12.27317648719798</v>
+        <v>-13.25792485948395</v>
       </c>
       <c r="F46">
-        <v>-1.284608653131841</v>
+        <v>-0.7698155430827555</v>
       </c>
       <c r="G46">
-        <v>-8.316833107518352</v>
+        <v>-7.442514720051292</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.625256345258092</v>
       </c>
       <c r="E47">
-        <v>-12.63786355598369</v>
+        <v>-12.53725444895528</v>
       </c>
       <c r="F47">
-        <v>-1.217057261014686</v>
+        <v>-0.8804374012762008</v>
       </c>
       <c r="G47">
-        <v>-7.437929614479402</v>
+        <v>-7.419953352201159</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.482299403092344</v>
       </c>
       <c r="E48">
-        <v>-11.27272789552742</v>
+        <v>-12.17315608179057</v>
       </c>
       <c r="F48">
-        <v>-1.37666789429042</v>
+        <v>-0.9302402011990252</v>
       </c>
       <c r="G48">
-        <v>-7.990923141359262</v>
+        <v>-7.203718449212584</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.353674775344434</v>
       </c>
       <c r="E49">
-        <v>-11.37171580886108</v>
+        <v>-13.6200352265593</v>
       </c>
       <c r="F49">
-        <v>-1.646471201456515</v>
+        <v>-1.458582707207652</v>
       </c>
       <c r="G49">
-        <v>-7.7224743141253</v>
+        <v>-9.056855904639338</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.244947982044215</v>
       </c>
       <c r="E50">
-        <v>-10.63478364817086</v>
+        <v>-11.71240649388015</v>
       </c>
       <c r="F50">
-        <v>-1.405225279357624</v>
+        <v>-1.37634481828367</v>
       </c>
       <c r="G50">
-        <v>-7.466022903925658</v>
+        <v>-7.818552966766029</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.169648042074702</v>
       </c>
       <c r="E51">
-        <v>-10.64306622713089</v>
+        <v>-13.0847333710606</v>
       </c>
       <c r="F51">
-        <v>-1.476521344111835</v>
+        <v>-1.782932805366271</v>
       </c>
       <c r="G51">
-        <v>-8.567504305206427</v>
+        <v>-7.445818644499486</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.136956318965867</v>
       </c>
       <c r="E52">
-        <v>-9.585889441566238</v>
+        <v>-12.03631012575278</v>
       </c>
       <c r="F52">
-        <v>-1.93200545948067</v>
+        <v>-1.463066970507219</v>
       </c>
       <c r="G52">
-        <v>-7.72374556361238</v>
+        <v>-8.253032273885518</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.15154571244866</v>
       </c>
       <c r="E53">
-        <v>-9.539096719644979</v>
+        <v>-10.8523632388174</v>
       </c>
       <c r="F53">
-        <v>-1.475003361991886</v>
+        <v>-1.868885276514916</v>
       </c>
       <c r="G53">
-        <v>-7.67468658926592</v>
+        <v>-8.498605231443115</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.220254124446875</v>
       </c>
       <c r="E54">
-        <v>-9.59636380194598</v>
+        <v>-9.207626007705533</v>
       </c>
       <c r="F54">
-        <v>-1.800703569443417</v>
+        <v>-1.604897337470314</v>
       </c>
       <c r="G54">
-        <v>-8.592124832381987</v>
+        <v>-8.224048447689199</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.350054485772259</v>
       </c>
       <c r="E55">
-        <v>-8.21650154401676</v>
+        <v>-9.130587607887044</v>
       </c>
       <c r="F55">
-        <v>-1.916407539919507</v>
+        <v>-1.482963067922885</v>
       </c>
       <c r="G55">
-        <v>-7.964802937054412</v>
+        <v>-8.488753047918244</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.539105124097858</v>
       </c>
       <c r="E56">
-        <v>-8.330338323621577</v>
+        <v>-9.689935660366471</v>
       </c>
       <c r="F56">
-        <v>-1.878488869186141</v>
+        <v>-1.708552473341742</v>
       </c>
       <c r="G56">
-        <v>-8.168828548094156</v>
+        <v>-8.119786126475391</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.777567497009442</v>
       </c>
       <c r="E57">
-        <v>-7.904702523166633</v>
+        <v>-8.433890938754976</v>
       </c>
       <c r="F57">
-        <v>-1.807204682226296</v>
+        <v>-1.619471391157146</v>
       </c>
       <c r="G57">
-        <v>-7.93937463676727</v>
+        <v>-7.496340879974303</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.062682324787735</v>
       </c>
       <c r="E58">
-        <v>-7.843912288087666</v>
+        <v>-8.101750012662393</v>
       </c>
       <c r="F58">
-        <v>-2.101187219456363</v>
+        <v>-1.594743406993474</v>
       </c>
       <c r="G58">
-        <v>-8.15150446328715</v>
+        <v>-8.666049314273913</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.384590355808877</v>
       </c>
       <c r="E59">
-        <v>-7.908465685067007</v>
+        <v>-8.277078940817367</v>
       </c>
       <c r="F59">
-        <v>-1.853815522876552</v>
+        <v>-1.774759299136688</v>
       </c>
       <c r="G59">
-        <v>-7.270720580381893</v>
+        <v>-8.199222666690204</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.728914597151245</v>
       </c>
       <c r="E60">
-        <v>-7.902356773630659</v>
+        <v>-7.990249925645533</v>
       </c>
       <c r="F60">
-        <v>-2.109017853355253</v>
+        <v>-2.029501563046954</v>
       </c>
       <c r="G60">
-        <v>-7.562925882405664</v>
+        <v>-7.281969814124337</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.089675516714419</v>
       </c>
       <c r="E61">
-        <v>-7.434148789029606</v>
+        <v>-8.65180563647808</v>
       </c>
       <c r="F61">
-        <v>-2.133868574727371</v>
+        <v>-1.800350403024274</v>
       </c>
       <c r="G61">
-        <v>-8.186573072184649</v>
+        <v>-7.557787915728715</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.460046743111377</v>
       </c>
       <c r="E62">
-        <v>-8.125135052438003</v>
+        <v>-8.722341147621554</v>
       </c>
       <c r="F62">
-        <v>-2.072252120528326</v>
+        <v>-1.866249989871624</v>
       </c>
       <c r="G62">
-        <v>-8.013540788483562</v>
+        <v>-9.044593643961877</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.829853603142816</v>
       </c>
       <c r="E63">
-        <v>-6.769767310416272</v>
+        <v>-8.381079874877523</v>
       </c>
       <c r="F63">
-        <v>-1.94969862196796</v>
+        <v>-2.131449463941537</v>
       </c>
       <c r="G63">
-        <v>-8.144290784557077</v>
+        <v>-8.551242905517528</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.189959611363475</v>
       </c>
       <c r="E64">
-        <v>-6.814277681437664</v>
+        <v>-7.34414083965315</v>
       </c>
       <c r="F64">
-        <v>-2.142995471918049</v>
+        <v>-1.614994254534198</v>
       </c>
       <c r="G64">
-        <v>-8.251191610565684</v>
+        <v>-7.601222273203954</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.535409328107635</v>
       </c>
       <c r="E65">
-        <v>-6.69818119330302</v>
+        <v>-6.969174134870029</v>
       </c>
       <c r="F65">
-        <v>-2.000508658853004</v>
+        <v>-2.33013091400412</v>
       </c>
       <c r="G65">
-        <v>-7.707845013387261</v>
+        <v>-8.16763013060894</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.856270492609053</v>
       </c>
       <c r="E66">
-        <v>-6.700132965600325</v>
+        <v>-7.254096662484632</v>
       </c>
       <c r="F66">
-        <v>-2.627114573943945</v>
+        <v>-2.069639005767851</v>
       </c>
       <c r="G66">
-        <v>-8.278900876729383</v>
+        <v>-8.666307536825975</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.139071833874032</v>
       </c>
       <c r="E67">
-        <v>-6.882218376974743</v>
+        <v>-7.545191500171691</v>
       </c>
       <c r="F67">
-        <v>-2.435989776656881</v>
+        <v>-1.658071847287109</v>
       </c>
       <c r="G67">
-        <v>-7.478493728972092</v>
+        <v>-8.825667267449873</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.382199902100202</v>
       </c>
       <c r="E68">
-        <v>-5.998314592365581</v>
+        <v>-8.114171616865432</v>
       </c>
       <c r="F68">
-        <v>-2.180401813787771</v>
+        <v>-2.022719342464084</v>
       </c>
       <c r="G68">
-        <v>-8.237601821126976</v>
+        <v>-8.039809967337678</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.580265595865905</v>
       </c>
       <c r="E69">
-        <v>-6.196208906500775</v>
+        <v>-7.587279137598979</v>
       </c>
       <c r="F69">
-        <v>-1.98947735529901</v>
+        <v>-1.84913488004347</v>
       </c>
       <c r="G69">
-        <v>-7.396087629408553</v>
+        <v>-8.078632734876711</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.725043458666864</v>
       </c>
       <c r="E70">
-        <v>-5.063646614130435</v>
+        <v>-8.118777074931234</v>
       </c>
       <c r="F70">
-        <v>-2.095405901012051</v>
+        <v>-2.500081563201758</v>
       </c>
       <c r="G70">
-        <v>-7.525669002906707</v>
+        <v>-8.261219253004136</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.816385510057025</v>
       </c>
       <c r="E71">
-        <v>-6.447407888180258</v>
+        <v>-7.648096543521992</v>
       </c>
       <c r="F71">
-        <v>-2.448770283394478</v>
+        <v>-2.297774218445777</v>
       </c>
       <c r="G71">
-        <v>-7.822720943599971</v>
+        <v>-7.335802595138425</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.856374237446474</v>
       </c>
       <c r="E72">
-        <v>-6.442068817325215</v>
+        <v>-8.087349465318001</v>
       </c>
       <c r="F72">
-        <v>-2.393121233084809</v>
+        <v>-1.787934148647228</v>
       </c>
       <c r="G72">
-        <v>-8.329442975477436</v>
+        <v>-8.230527185309553</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.845193710105347</v>
       </c>
       <c r="E73">
-        <v>-6.639818220292164</v>
+        <v>-7.411424906459116</v>
       </c>
       <c r="F73">
-        <v>-2.315476091315601</v>
+        <v>-2.015094590334201</v>
       </c>
       <c r="G73">
-        <v>-7.842882165934133</v>
+        <v>-8.338596633893522</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.783927059385212</v>
       </c>
       <c r="E74">
-        <v>-6.794053516519408</v>
+        <v>-7.766579537458679</v>
       </c>
       <c r="F74">
-        <v>-2.712210260192337</v>
+        <v>-1.879283889555691</v>
       </c>
       <c r="G74">
-        <v>-7.851277709421724</v>
+        <v>-8.376472585408322</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.681501195046126</v>
       </c>
       <c r="E75">
-        <v>-7.573607674569822</v>
+        <v>-9.767775600084317</v>
       </c>
       <c r="F75">
-        <v>-2.330539510130303</v>
+        <v>-2.742851010391302</v>
       </c>
       <c r="G75">
-        <v>-7.21377588656089</v>
+        <v>-8.286104623822837</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.542997280807031</v>
       </c>
       <c r="E76">
-        <v>-7.747976566235169</v>
+        <v>-7.627790866071599</v>
       </c>
       <c r="F76">
-        <v>-2.729305573696548</v>
+        <v>-2.382382123272214</v>
       </c>
       <c r="G76">
-        <v>-7.611279710552259</v>
+        <v>-7.95200105745405</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.368054983359466</v>
       </c>
       <c r="E77">
-        <v>-7.23501367301631</v>
+        <v>-10.5912378421131</v>
       </c>
       <c r="F77">
-        <v>-2.878473250165874</v>
+        <v>-2.047623909837327</v>
       </c>
       <c r="G77">
-        <v>-7.696953318563058</v>
+        <v>-7.996756322599457</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.167237868514187</v>
       </c>
       <c r="E78">
-        <v>-8.462397682633259</v>
+        <v>-8.523844546443339</v>
       </c>
       <c r="F78">
-        <v>-2.485273912892399</v>
+        <v>-2.363991338329173</v>
       </c>
       <c r="G78">
-        <v>-8.041051421914906</v>
+        <v>-9.101399294870232</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.945693207681124</v>
       </c>
       <c r="E79">
-        <v>-8.737144729152629</v>
+        <v>-10.67374211005885</v>
       </c>
       <c r="F79">
-        <v>-2.956419296059015</v>
+        <v>-2.453181696221934</v>
       </c>
       <c r="G79">
-        <v>-7.521507647163842</v>
+        <v>-7.730174643049645</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.703238815291973</v>
       </c>
       <c r="E80">
-        <v>-9.582443272846401</v>
+        <v>-10.25488543519339</v>
       </c>
       <c r="F80">
-        <v>-3.224173287770532</v>
+        <v>-2.172818238011689</v>
       </c>
       <c r="G80">
-        <v>-8.256362682698025</v>
+        <v>-8.256034938689638</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.443810766046688</v>
       </c>
       <c r="E81">
-        <v>-9.281707313997012</v>
+        <v>-11.08946960938501</v>
       </c>
       <c r="F81">
-        <v>-3.167818696475535</v>
+        <v>-2.851241426949893</v>
       </c>
       <c r="G81">
-        <v>-7.878662542122576</v>
+        <v>-7.698449685146809</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.172970071950331</v>
       </c>
       <c r="E82">
-        <v>-9.667075923575752</v>
+        <v>-11.92855055826625</v>
       </c>
       <c r="F82">
-        <v>-3.088432270052301</v>
+        <v>-2.640870643525452</v>
       </c>
       <c r="G82">
-        <v>-7.783481047322989</v>
+        <v>-7.253479259213369</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.891831428462767</v>
       </c>
       <c r="E83">
-        <v>-11.99867397827503</v>
+        <v>-12.73513064919444</v>
       </c>
       <c r="F83">
-        <v>-3.491959745453315</v>
+        <v>-3.241910794023454</v>
       </c>
       <c r="G83">
-        <v>-7.577697536601892</v>
+        <v>-7.574370438334925</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.598469859873668</v>
       </c>
       <c r="E84">
-        <v>-11.65585491047236</v>
+        <v>-14.3510532001955</v>
       </c>
       <c r="F84">
-        <v>-3.476392708157503</v>
+        <v>-3.028812077159668</v>
       </c>
       <c r="G84">
-        <v>-7.358317615351009</v>
+        <v>-8.331591519532424</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.298210765656085</v>
       </c>
       <c r="E85">
-        <v>-12.84773115539516</v>
+        <v>-13.71967976862408</v>
       </c>
       <c r="F85">
-        <v>-3.465432671369704</v>
+        <v>-3.114712286013103</v>
       </c>
       <c r="G85">
-        <v>-7.628640211360198</v>
+        <v>-7.961939315162942</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.991535386748303</v>
       </c>
       <c r="E86">
-        <v>-14.53266765027312</v>
+        <v>-15.91879731622896</v>
       </c>
       <c r="F86">
-        <v>-3.857257351908578</v>
+        <v>-2.801470301145377</v>
       </c>
       <c r="G86">
-        <v>-7.51583999320061</v>
+        <v>-8.131618016232748</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.674081065994191</v>
       </c>
       <c r="E87">
-        <v>-15.4788696518058</v>
+        <v>-17.0519528386943</v>
       </c>
       <c r="F87">
-        <v>-3.76703441775895</v>
+        <v>-3.581694898180987</v>
       </c>
       <c r="G87">
-        <v>-6.889325870984616</v>
+        <v>-8.529224467135835</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.351256599957368</v>
       </c>
       <c r="E88">
-        <v>-16.82427927948467</v>
+        <v>-17.81683021248586</v>
       </c>
       <c r="F88">
-        <v>-3.652793791548726</v>
+        <v>-3.054126032512052</v>
       </c>
       <c r="G88">
-        <v>-7.339973882517907</v>
+        <v>-6.577220879724286</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.026885554654647</v>
       </c>
       <c r="E89">
-        <v>-17.47685955483401</v>
+        <v>-19.64784169342924</v>
       </c>
       <c r="F89">
-        <v>-3.913467034112312</v>
+        <v>-3.6273832301355</v>
       </c>
       <c r="G89">
-        <v>-7.418284837249367</v>
+        <v>-8.225958632465359</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.702747115628714</v>
       </c>
       <c r="E90">
-        <v>-18.8195656835303</v>
+        <v>-21.70183070603629</v>
       </c>
       <c r="F90">
-        <v>-4.072131403103571</v>
+        <v>-3.84590455605375</v>
       </c>
       <c r="G90">
-        <v>-7.375820469617135</v>
+        <v>-6.775241161155792</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.38582017411195</v>
       </c>
       <c r="E91">
-        <v>-21.26535826728099</v>
+        <v>-22.77723459948182</v>
       </c>
       <c r="F91">
-        <v>-4.511658889521397</v>
+        <v>-3.606665189349721</v>
       </c>
       <c r="G91">
-        <v>-7.485197583689116</v>
+        <v>-8.129906464188943</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.088796521059535</v>
       </c>
       <c r="E92">
-        <v>-23.42501922085704</v>
+        <v>-24.42679012693785</v>
       </c>
       <c r="F92">
-        <v>-3.945134025744482</v>
+        <v>-4.026023389081467</v>
       </c>
       <c r="G92">
-        <v>-7.370934104401171</v>
+        <v>-8.176396455196929</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.822823334539497</v>
       </c>
       <c r="E93">
-        <v>-25.76039402287871</v>
+        <v>-27.55491506026829</v>
       </c>
       <c r="F93">
-        <v>-4.369314609988741</v>
+        <v>-3.503109826950966</v>
       </c>
       <c r="G93">
-        <v>-8.294712042224942</v>
+        <v>-7.248241976170242</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.597200919503461</v>
       </c>
       <c r="E94">
-        <v>-27.26924533444242</v>
+        <v>-28.85170246252679</v>
       </c>
       <c r="F94">
-        <v>-4.138037324774584</v>
+        <v>-3.116963523971901</v>
       </c>
       <c r="G94">
-        <v>-7.407671228250464</v>
+        <v>-7.916852995463608</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.429807152803217</v>
       </c>
       <c r="E95">
-        <v>-28.78873855992414</v>
+        <v>-30.93603677945925</v>
       </c>
       <c r="F95">
-        <v>-4.206300592700728</v>
+        <v>-3.92054144843658</v>
       </c>
       <c r="G95">
-        <v>-8.313016048511573</v>
+        <v>-7.814044003741541</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.340664608205025</v>
       </c>
       <c r="E96">
-        <v>-32.4696520511339</v>
+        <v>-32.52959093309942</v>
       </c>
       <c r="F96">
-        <v>-4.136642079863082</v>
+        <v>-3.61482602593198</v>
       </c>
       <c r="G96">
-        <v>-8.673680121741933</v>
+        <v>-7.742079364808863</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.331679657595675</v>
       </c>
       <c r="E97">
-        <v>-34.8869899684574</v>
+        <v>-36.99141486032489</v>
       </c>
       <c r="F97">
-        <v>-4.501821700227644</v>
+        <v>-3.62078867870361</v>
       </c>
       <c r="G97">
-        <v>-8.726840862011549</v>
+        <v>-8.764183815694528</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.432339684182143</v>
       </c>
       <c r="E98">
-        <v>-37.57624463604547</v>
+        <v>-38.54760231069077</v>
       </c>
       <c r="F98">
-        <v>-4.212207815765317</v>
+        <v>-3.712189098201367</v>
       </c>
       <c r="G98">
-        <v>-8.820790833870527</v>
+        <v>-8.477533609085654</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.632334807648554</v>
       </c>
       <c r="E99">
-        <v>-38.7627591677432</v>
+        <v>-41.67494381801788</v>
       </c>
       <c r="F99">
-        <v>-4.36067866163185</v>
+        <v>-3.536307470350408</v>
       </c>
       <c r="G99">
-        <v>-9.085184242818881</v>
+        <v>-8.615669432257285</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.968804596466324</v>
       </c>
       <c r="E100">
-        <v>-42.48291641470342</v>
+        <v>-44.23733328628107</v>
       </c>
       <c r="F100">
-        <v>-4.461800659891532</v>
+        <v>-3.373300579739014</v>
       </c>
       <c r="G100">
-        <v>-9.684475749065447</v>
+        <v>-9.208862913620512</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.380416903563588</v>
       </c>
       <c r="E101">
-        <v>-45.05631233904226</v>
+        <v>-47.02354711084737</v>
       </c>
       <c r="F101">
-        <v>-4.481189971414257</v>
+        <v>-3.627351556017191</v>
       </c>
       <c r="G101">
-        <v>-10.77083457832283</v>
+        <v>-9.593170903092348</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.949605613512704</v>
       </c>
       <c r="E102">
-        <v>-48.32349538796323</v>
+        <v>-48.82980368862783</v>
       </c>
       <c r="F102">
-        <v>-3.910956068383383</v>
+        <v>-3.572372413309753</v>
       </c>
       <c r="G102">
-        <v>-10.79919602195776</v>
+        <v>-9.795110870442352</v>
       </c>
     </row>
   </sheetData>
